--- a/data/describe/few_shot/final_summary/messages_personality.xlsx
+++ b/data/describe/few_shot/final_summary/messages_personality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\input_final_summary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\final_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5EE2F05-B3BB-40EC-BF3F-A02AF4402A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9ADF3D9-05A9-4E28-96AC-C9F993C82ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51930" yWindow="2895" windowWidth="27195" windowHeight="17070"/>
+    <workbookView xWindow="54660" yWindow="3135" windowWidth="22980" windowHeight="17070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QandA_data" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>User</t>
   </si>
@@ -177,21 +177,6 @@
     <t>A person described as fluid and shifting tends to have moods that change quite often.</t>
   </si>
   <si>
-    <t xml:space="preserve">Now your task is to provide a description of a cluster.
-You will receive information about the cluster based on the latent factors that best describe it.
-For each cluster, write a concise summary based on the available information.
-The first sentence should give an overview of the cluster. 
-The second sentence should describe the cluster’s specific strengths based on the available information.
-The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-I will provided you with the cluster description and you will return the summary. </t>
-  </si>
-  <si>
-    <t>Understood. Please provide the cluster descriptions.</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:```Members of this cluster can be described as:  relatively high on social and engaging,  normal on thoughtful and visionary,  normal on unassuming and orderly,  normal on caring and down-to-earth,  normal on self-reliant and systematic,  slightly high on methodical and diligent,  relatively high on creative and inventive,  slightly high on concrete and routine,  normal on proactive and organized,  relatively high on calm demeanor,  normal on compassionate,  relatively low on steady and composed´´´</t>
-  </si>
-  <si>
     <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:```Members of this cluster can be described as:  relatively low on private and sensitive,  normal on carefree and practical,  relatively low on unassuming and orderly,  slightly low on articulate intellect,  relatively high on concerned and prudent,  slightly low on easygoing and flexible,  normal on verbal and literal,  normal on abstract and spontaneous,  slightly low on unplanned and adaptive,  normal on responsive psyche,  slightly low on compassionate,  slightly low on steady and composed´´´</t>
   </si>
   <si>
@@ -205,21 +190,6 @@
   </si>
   <si>
     <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:```Members of this cluster can be described as:  relatively low on private and sensitive,  normal on carefree and practical,  relatively high on vivacious and outspoken,  slightly low on articulate intellect,  quite low on self-reliant and systematic,  normal on methodical and diligent,  relatively high on creative and inventive,  normal on abstract and spontaneous,  normal on unplanned and adaptive,  normal on calm demeanor,  slightly low on compassionate,  slightly high on fluid and shifting´´´</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are highly sociable and creatively inventive, preferring methodical and practical approaches, and maintaining a calm demeanor despite internal emotional shifts.
-Their strengths are evident in their engaging social presence, their abundant and inventive ideas often applied in a thoughtful and practical manner, and their diligent, structured approach to tasks, all supported by a generally unruffled disposition.
-A significant weakness, however, is their relatively low level of steadiness and composure, indicating that their moods can often shift dramatically.</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are less reserved and more prone to worry, balancing a degree of conscientiousness with a less empathetic and emotionally stable state.
-Their strengths include being less private or easily irritated, a tendency to be more proactive and organized, and a reduced likelihood of being messy or shirking duties.
-However, they frequently find themselves pondering and worrying, are less compassionate and thoughtful, exhibit less stable moods, and may not be as articulate or quick to grasp complex ideas.</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are outwardly social, practical, and highly organized, yet they grapple with an internal tension between a calm demeanor and frequently shifting moods, often experiencing concern despite a generally carefree exterior.
-Their strengths lie in their strong social engagement, vivaciousness, and proactive, organized approach to life, ensuring they are prepared and thrive in structured, concrete environments.
-However, they are prone to worry and internal mood shifts, exhibiting a relative inflexibility, and their literal nature means they are less inclined towards abstract or imaginative thinking.</t>
   </si>
   <si>
     <t>This cluster describes individuals who are sociable and practical, demonstrating a strong drive for organized action, coupled with a calm and rational demeanor.
@@ -230,11 +200,6 @@
     <t>This cluster describes individuals who are highly sociable, vivacious, and meticulously organized, yet they are also prone to worrying and frequent mood shifts, with a very practical and less imaginative approach to life.
 Their strengths include an exceptional ability to engage others, light up a room, and proactively ensure tasks are methodically completed and they are always prepared, alongside a practical mindset that keeps them from dwelling on minor details.
 However, they exhibit weaknesses in intellectual articulation and abstract thinking, often struggling with complex ideas and lacking a vivid imagination, while their tendency to worry and experience fluid emotional shifts can create internal inconsistency despite their organized efforts.</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are highly energetic, outgoing, and brimming with creative ideas, though they may face challenges in systematic organization and emotional consistency.
-Their strengths lie in their vivacious and outspoken nature, making them the life of the party and confidently expressive, combined with a remarkable ability to generate inventive and excellent ideas.
-However, they exhibit weaknesses in being self-reliant and systematic, potentially leading to disorganization, coupled with less articulate intellectual expression, lower compassion, and a tendency for their moods to shift frequently.</t>
   </si>
   <si>
     <t>Fantastic! That’s exactly what I needed. Now, let’s return to your analysis. Your next task is to describe a specific person based on the provided information. Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the person. The first sentence should use varied language to give an overview of the person. The second sentence should describe the person's specific strengths based on the metrics. The third sentence should describe aspects in which the person is average and/or weak based on the statistics. Finally, summarize the person with a single concluding statement.
@@ -255,11 +220,42 @@
   <si>
     <t>Person №18 is a diligent yet often anxious individual who thrives on routine and concrete thinking, though their emotional state can be quite changeable. Their strengths include a less private nature, a methodical adherence to responsibilities, and a highly prudent approach to anticipating potential concerns, suggesting a reliable and conscientious character. However, they are significantly lacking in imaginative and visionary ideas, show low compassion, and exhibit frequent, fluid mood shifts. Overall, Person №18 is a practical and conscientious worrier who prefers structure and anticipates problems, but struggles with creativity, emotional warmth, and consistent emotional stability.</t>
   </si>
+  <si>
+    <t>Thats really good. You truly understand the factors and names. 
+Now your task is to provide a description of a cluster.
+Please use the statistical description enclosed with ``` ´´´ . It provides information about the cluster based on the latent factors that most accurately describe it.
+For each cluster, write a concise summary based on the available information.
+The first sentence should give an overview of the cluster. 
+The second sentence should describe the cluster’s specific strengths based on the available information.
+The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
+I will provided you with the cluster description and you will return the summary. 
+Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:```Members of this cluster can be described as:  relatively high on social and engaging,  normal on thoughtful and visionary,  normal on unassuming and orderly,  normal on caring and down-to-earth,  normal on self-reliant and systematic,  slightly high on methodical and diligent,  relatively high on creative and inventive,  slightly high on concrete and routine,  normal on proactive and organized,  relatively high on calm demeanor,  normal on compassionate,  relatively low on steady and composed´´´</t>
+  </si>
+  <si>
+    <t>This cluster describes individuals who are highly sociable and creatively inventive, preferring methodical and practical approaches, and maintaining a calm demeanor despite internal emotional shifts.
+Their strengths are evident in their engaging social presence, their abundant and inventive ideas often applied in a thoughtful and practical manner, and their diligent, structured approach to tasks, all supported by a generally unruffled disposition.
+A significant weakness, however, is their relatively low level of steadiness and composure, indicating that their moods can often shift dramatically.</t>
+  </si>
+  <si>
+    <t>This cluster describes individuals who are less reserved and more prone to worry, balancing a degree of conscientiousness with a less empathetic and emotionally stable state.
+Their strengths include being less private or easily irritated, a tendency to be more proactive and organized, and a reduced likelihood of being messy or shirking duties.
+However, they frequently find themselves pondering and worrying, are less compassionate and thoughtful, exhibit less stable moods, and may not be as articulate or quick to grasp complex ideas.</t>
+  </si>
+  <si>
+    <t>This cluster describes individuals who are outwardly social, practical, and highly organized, yet they grapple with an internal tension between a calm demeanor and frequently shifting moods, often experiencing concern despite a generally carefree exterior.
+Their strengths lie in their strong social engagement, vivaciousness, and proactive, organized approach to life, ensuring they are prepared and thrive in structured, concrete environments.
+However, they are prone to worry and internal mood shifts, exhibiting a relative inflexibility, and their literal nature means they are less inclined towards abstract or imaginative thinking.</t>
+  </si>
+  <si>
+    <t>This cluster describes individuals who are highly energetic, outgoing, and brimming with creative ideas, though they may face challenges in systematic organization and emotional consistency.
+Their strengths lie in their vivacious and outspoken nature, making them the life of the party and confidently expressive, combined with a remarkable ability to generate inventive and excellent ideas.
+However, they exhibit weaknesses in being self-reliant and systematic, potentially leading to disorganization, coupled with less articulate intellectual expression, lower compassion, and a tendency for their moods to shift frequently.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -737,7 +733,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -745,9 +741,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1103,8 +1096,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="62.453125" customWidth="1"/>
@@ -1311,76 +1304,68 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="174" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" ht="333.5" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="B27" s="3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="145" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="145" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="B31" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>57</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="362.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/data/describe/few_shot/final_summary/messages_personality.xlsx
+++ b/data/describe/few_shot/final_summary/messages_personality.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\final_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9ADF3D9-05A9-4E28-96AC-C9F993C82ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D838DE5-07C9-4A9E-B0BB-FC69FFE86AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="54660" yWindow="3135" windowWidth="22980" windowHeight="17070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31005" yWindow="2295" windowWidth="29250" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="QandA_data" sheetId="1" r:id="rId1"/>
+    <sheet name="messages_personality1.xlsx" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -36,227 +36,205 @@
     <t>What does it mean when a person is described as private and sensitive?</t>
   </si>
   <si>
-    <t>A private and sensitive person is easily irritated and tends to keep in the background, often showing little interest in others. They can also frequently feel blue and get upset quite easily.</t>
+    <t>Someone who is private and sensitive might find themselves easily irritated, preferring to keep to themselves and showing little interest in others. This person also tends to feel blue and can get upset quite easily.</t>
   </si>
   <si>
     <t>What does it mean when a person is described as social and engaging?</t>
   </si>
   <si>
-    <t>When someone is described as social and engaging, it means they feel very comfortable around people and love to chat with many different individuals at parties. They are also keen to start conversations, often becoming the life of the party, and genuinely interested in others.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as thoughtful and visionary?</t>
-  </si>
-  <si>
-    <t>When a person is described as thoughtful and visionary, it means they are brimming with excellent and plentiful ideas, often springing from a vivid imagination, though they might also find themselves worrying about things. They also have a keen eye for details, ensuring their grand visions are well-considered.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as carefree and practical?</t>
-  </si>
-  <si>
-    <t>A carefree and practical person typically doesn't dwell on worries and isn't known for a particularly vivid imagination. They also aren't usually overflowing with new or excellent ideas, nor do they meticulously focus on every little detail.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as unassuming and orderly?</t>
-  </si>
-  <si>
-    <t>When a person is described as unassuming and orderly, it means they strongly prefer to stay out of the spotlight, are generally quiet when meeting new people, and are quite prompt in getting their chores done. They also tend to be relaxed most of the time and thoughtfully make time to help others.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as vivacious and outspoken?</t>
-  </si>
-  <si>
-    <t>A vivacious and outspoken individual often lights up a room, becoming the life of the party, and isn't shy about speaking their mind, even if it means occasionally insulting others. They might also be a bit disorganised, frequently forgetting where things go, making a mess, or leaving their belongings scattered.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as articulate intellect?</t>
-  </si>
-  <si>
-    <t>When someone is described as an articulate intellect, they possess a truly rich vocabulary and frequently employ more challenging words, showcasing their depth of thought. They are often bubbling over with ideas and quick to understand complex concepts, though they might not always be deeply engaged with the concerns of others.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as caring and down-to-earth?</t>
-  </si>
-  <si>
-    <t>A person described as caring and down-to-earth genuinely feels the emotions of others, takes time out to help them, and easily sympathizes with their feelings. They are not particularly interested in abstract ideas, sometimes finding them a bit challenging to understand.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as self-reliant and systematic?</t>
-  </si>
-  <si>
-    <t>When someone is described as self-reliant and systematic, it means they are generally relaxed and comfortable taking the lead in conversations. They have a strong appreciation for order and structure, and tend to keep a slight distance, not getting overly involved in other people's concerns or problems.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as concerned and prudent?</t>
-  </si>
-  <si>
-    <t>When a person is described as concerned and prudent, it means they are the kind of individual who often finds themselves pondering and worrying about things.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as easygoing and flexible?</t>
-  </si>
-  <si>
-    <t>Easygoing and flexible individuals might often forget to put things away, tending to make a bit of a mess and leave their belongings scattered around. What's more, they generally sail through life feeling relaxed and might even be found shirking a duty or two!</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as methodical and diligent?</t>
-  </si>
-  <si>
-    <t>When a person is described as methodical and diligent, it means they have a thoughtful approach to their tasks. They tend to follow a schedule, get chores done promptly, and are always ready for what comes next, showcasing a commitment to being organized and responsible.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as verbal and literal?</t>
-  </si>
-  <si>
-    <t>When a person is described as verbal and literal, it suggests they have a rich vocabulary and often use complex words, yet they may not possess a strong imagination. Their communication style tends to be straightforward, focusing on clear and precise language rather than creativity or inventive thinking.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as creative and inventive?</t>
-  </si>
-  <si>
-    <t>When a person is described as creative and inventive, it means they are brimming with ideas and often have excellent concepts that showcase their vivid imagination. They bring a unique flair to their thoughts, demonstrating an ability to think outside the box and generate innovative solutions.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as abstract and spontaneous?</t>
-  </si>
-  <si>
-    <t>When a person is described as abstract and spontaneous, it means they embrace creativity and are open to new ideas, often thriving on unpredictability. They are not bound by rigid routines or schedules and can easily grasp abstract concepts, showing a lively imagination and a willingness to explore the unconventional.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as concrete and routine?</t>
-  </si>
-  <si>
-    <t>When a person is described as concrete and routine, they tend to steer clear of abstract ideas and often follow a structured schedule. Their focus is on the tangible and practical aspects of life, and they may struggle with imaginative thinking or understanding abstract concepts.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as unplanned and adaptive?</t>
-  </si>
-  <si>
-    <t>When a person is described as unplanned and adaptive, it means they are not proactive or organized. Instead of sticking to a rigid schedule or plan, they are flexible and able to adjust to whatever comes their way, embracing spontaneity in life.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as proactive and organized?</t>
-  </si>
-  <si>
-    <t>A proactive and organized person is someone who truly shines when it comes to being always prepared!</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as responsive psyche?</t>
-  </si>
-  <si>
-    <t>A person with a responsive psyche is easily stirred, meaning little things can readily upset their equilibrium.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as calm demeanor?</t>
-  </si>
-  <si>
-    <t>A person with a calm demeanor is simply someone who isn't easily disturbed.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as compassionate?</t>
-  </si>
-  <si>
-    <t>When a person is described as compassionate, it means they have a wonderfully soft heart.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as rational and resolute?</t>
-  </si>
-  <si>
-    <t>When a person is described as rational and resolute, it means they are not easily swayed by sentiment and certainly don't have a soft heart.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as steady and composed?</t>
-  </si>
-  <si>
-    <t>When a person is described as steady and composed, it means their moods don't often shift dramatically.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as fluid and shifting?</t>
-  </si>
-  <si>
-    <t>A person described as fluid and shifting tends to have moods that change quite often.</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:```Members of this cluster can be described as:  relatively low on private and sensitive,  normal on carefree and practical,  relatively low on unassuming and orderly,  slightly low on articulate intellect,  relatively high on concerned and prudent,  slightly low on easygoing and flexible,  normal on verbal and literal,  normal on abstract and spontaneous,  slightly low on unplanned and adaptive,  normal on responsive psyche,  slightly low on compassionate,  slightly low on steady and composed´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:```Members of this cluster can be described as:  slightly high on social and engaging,  slightly high on carefree and practical,  slightly high on vivacious and outspoken,  normal on caring and down-to-earth,  slightly high on concerned and prudent,  relatively low on easygoing and flexible,  normal on verbal and literal,  relatively high on concrete and routine,  relatively high on proactive and organized,  slightly high on calm demeanor,  normal on rational and resolute,  relatively high on fluid and shifting´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:```Members of this cluster can be described as:  slightly high on social and engaging,  slightly low on thoughtful and visionary,  normal on unassuming and orderly,  slightly high on caring and down-to-earth,  normal on self-reliant and systematic,  slightly high on methodical and diligent,  slightly low on verbal and literal,  slightly low on abstract and spontaneous,  normal on unplanned and adaptive,  relatively low on responsive psyche,  relatively high on rational and resolute,  normal on steady and composed´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:```Members of this cluster can be described as:  relatively high on social and engaging,  extremely high on carefree and practical,  extremely high on vivacious and outspoken,  slightly low on articulate intellect,  extremely high on concerned and prudent,  extremely high on methodical and diligent,  normal on verbal and literal,  extremely low on abstract and spontaneous,  relatively high on proactive and organized,  normal on calm demeanor,  normal on compassionate,  relatively high on fluid and shifting´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:```Members of this cluster can be described as:  relatively low on private and sensitive,  normal on carefree and practical,  relatively high on vivacious and outspoken,  slightly low on articulate intellect,  quite low on self-reliant and systematic,  normal on methodical and diligent,  relatively high on creative and inventive,  normal on abstract and spontaneous,  normal on unplanned and adaptive,  normal on calm demeanor,  slightly low on compassionate,  slightly high on fluid and shifting´´´</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are sociable and practical, demonstrating a strong drive for organized action, coupled with a calm and rational demeanor.
-Their strengths lie in their ability to connect with people, showing genuine interest and care, while also being highly methodical, diligent, and emotionally stable, making them reliable and composed, and not easily swayed by sentiment.
-However, they may lack a vivid imagination and visionary thinking, struggle with abstract concepts or creative spontaneity, and tend to have a less rich or complex vocabulary, sometimes appearing less articulate.</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are highly sociable, vivacious, and meticulously organized, yet they are also prone to worrying and frequent mood shifts, with a very practical and less imaginative approach to life.
-Their strengths include an exceptional ability to engage others, light up a room, and proactively ensure tasks are methodically completed and they are always prepared, alongside a practical mindset that keeps them from dwelling on minor details.
-However, they exhibit weaknesses in intellectual articulation and abstract thinking, often struggling with complex ideas and lacking a vivid imagination, while their tendency to worry and experience fluid emotional shifts can create internal inconsistency despite their organized efforts.</t>
+    <t>A social and engaging person absolutely thrives in company, effortlessly feeling comfortable around people and striking up conversations with many at parties. They love to kick off discussions, often becoming the heart of the party, and genuinely enjoy learning about others.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as meticulous and inventive?</t>
+  </si>
+  <si>
+    <t>A meticulous and inventive person is absolutely bursting with excellent ideas and possesses a truly vivid imagination, often found brimming with new thoughts. They tend to worry about things and pay careful attention to all the little details.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as broad-minded and practical?</t>
+  </si>
+  <si>
+    <t>A person described as broad-minded and practical is not one to fret over things, nor do they often get lost in a vivid imagination or constantly burst forth with new concepts. Instead, they tend to be less focused on generating brilliant ideas or getting caught up in the minutiae of details.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as humble and orderly?</t>
+  </si>
+  <si>
+    <t>Humble and orderly individuals prefer to stay out of the spotlight, getting their chores done promptly, and maintaining a calm demeanor, especially when meeting new people. They also make a point of taking time out for others, demonstrating a considerate and composed nature.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as exuberant and direct?</t>
+  </si>
+  <si>
+    <t>When a person is described as exuberant and direct, they are often the life of the party and aren't afraid to speak their mind, even if it means occasionally insulting someone. You might also notice they have a habit of forgetting to put things back in their place, leaving belongings scattered, and generally making a bit of a mess.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as intellectual and expressive?</t>
+  </si>
+  <si>
+    <t>A person described as intellectual and expressive boasts a rich vocabulary, often utilizing difficult words to articulate their abundant ideas and quickly grasp new concepts. They are full of innovative thoughts, though their focus on ideas might mean they aren't always deeply interested in the feelings or experiences of others.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as empathetic and concrete?</t>
+  </si>
+  <si>
+    <t>An empathetic and concrete person truly feels and sympathizes with the emotions of others, always ready to take time out to help. They tend to shy away from abstract concepts, preferring to focus on practical, real-world ideas.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as self-possessed and systematic?</t>
+  </si>
+  <si>
+    <t>A self-possessed and systematic individual often comes across as quite relaxed, showing little interest in others or their problems. They are also known for liking order and are comfortable initiating conversations.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as thoughtful and vigilant?</t>
+  </si>
+  <si>
+    <t>When a person is described as thoughtful and vigilant, it means they are often someone who finds themselves wrapped up in worrying about various matters.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as easygoing and casual?</t>
+  </si>
+  <si>
+    <t>An easygoing and casual person might often forget where things go, leading to a bit of a mess and belongings left scattered around. They generally carry a relaxed demeanor, though they might occasionally shirk their duties.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as planned and prepared?</t>
+  </si>
+  <si>
+    <t>A person who is planned and prepared loves to stick to a schedule and tackles their chores without delay. They are also the kind of individual who is always ready for whatever comes their way.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as articulate and literal?</t>
+  </si>
+  <si>
+    <t>Someone described as articulate and literal possesses a rich vocabulary and enjoys using complex words to express themselves. Yet, when it comes to creativity, their imagination isn't particularly strong.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as imaginative and conceptual?</t>
+  </si>
+  <si>
+    <t>Someone who is imaginative and conceptual is truly a fount of creativity, always bubbling with a vivid imagination. They are also brimming with excellent and fresh ideas, constantly generating new thoughts and concepts.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as speculative and spontaneous?</t>
+  </si>
+  <si>
+    <t>A speculative and spontaneous person doesn't shy away from abstract ideas, finding them easy to understand and being genuinely interested in them, and they often possess a good imagination. You won't find them rigidly sticking to a schedule, as they prefer a more flexible approach to life.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as observant and routine?</t>
+  </si>
+  <si>
+    <t>When a person is described as observant and routine, they might find abstract ideas a bit of a puzzle and aren't typically known for a wild imagination. Instead, they prefer the comfort of sticking to a clear schedule and generally aren't very interested in exploring complex, abstract concepts.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as impromptu and bold?</t>
+  </si>
+  <si>
+    <t>When a person is described as impromptu and bold, it means they are not always prepared for what's ahead.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as foresighted and cautious?</t>
+  </si>
+  <si>
+    <t>When a person is described as foresighted and cautious, it means they are the kind of individual who is always prepared for what lies ahead.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as impressionable and reactive?</t>
+  </si>
+  <si>
+    <t>When a person is described as impressionable and reactive, it means they tend to be quite easily disturbed by things.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as unflappable and stable?</t>
+  </si>
+  <si>
+    <t>When a person is described as unflappable and stable, it means they are not easily disturbed by external events and maintain a calm demeanor even in challenging situations. This reliability suggests they approach life with a sense of consistency and steadiness, making them a soothing presence to those around them.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as kindly and warm?</t>
+  </si>
+  <si>
+    <t>When a person is described as kindly and warm, it means they tend to have a gentle and compassionate nature, showing care for othersâ€”even if those traits are not predominantly defined by strong characteristics. In contrast, they are not firm and objective, suggesting they may prioritize empathy and understanding over strictness or detachment.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as firm and objective?</t>
+  </si>
+  <si>
+    <t>When a person is described as firm and objective, it means they are not kindly and warm. They tend to approach situations with a level-headed and logical perspective, often making decisions based on facts rather than emotions, and can be unwavering in their stance.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as even temper?</t>
+  </si>
+  <si>
+    <t>When a person is described as having an even temper, it means they are not prone to mood swings or emotional ups and downs. They maintain a steady and calm demeanor, remaining composed even in situations that might provoke strong feelings in others.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as variable temper?</t>
+  </si>
+  <si>
+    <t>When a person is described as having a variable temper, it means they often find their mood shifting unpredictably. This can make their emotional responses feel a bit like a rollercoaster, keeping others on their toes and unsure of what to expect from them.</t>
+  </si>
+  <si>
+    <t>This cluster describes individuals who are highly sociable, imaginatively conceptual, and remarkably stable, though they may experience some emotional fluctuations. Their strengths shine through in their strong social engagement, a rich and imaginative conceptual mind that generates fresh ideas, and a notably unflappable and stable demeanor that keeps them calm and consistent. They also possess a slight inclination towards being planned and prepared. However, a relative weakness lies in their less even temper, suggesting they may be more prone to mood swings, and despite their imagination, they also show a slight tendency towards being observant and routine, which might imply a subtle disconnect in fully embracing abstract concepts.</t>
+  </si>
+  <si>
+    <t>This cluster describes individuals who are often preoccupied with worries, generally less private, and tend to be quite responsible, though not always warm or even-tempered. Their strengths include a thoughtful and vigilant nature, indicating attentiveness to potential issues, coupled with a tendency to be more prepared and responsible rather than casual or impulsive. However, they exhibit weaknesses in being less private and sensitive, less humble or orderly in their interactions, less intellectually expressive, less kindly or warm, and are prone to a more variable temper.</t>
+  </si>
+  <si>
+    <t>This cluster describes individuals who are socially engaging and well-prepared, embodying a stable yet sometimes unpredictable demeanor, with a preference for practical rather than abstract thought. Their specific strengths include their high sociability and engaging nature, consistently being foresighted and cautious in preparation, and maintaining an unflappable and stable temperament, while also showing empathy and a preference for concrete ideas. However, they exhibit weaknesses in being prone to worrying, can struggle with abstract ideas and a vivid imagination, and are characterized by a relatively high variable temper, suggesting unpredictable mood shifts.</t>
+  </si>
+  <si>
+    <t>This cluster describes individuals who are sociable and well-organized, demonstrating a stable and prepared approach to life, though they are less inclined towards abstract thought or intense imagination. Their specific strengths include being socially engaging, empathetically concrete, humble and orderly, and reliably planned and prepared, all supported by an unflappable and even-tempered nature. However, they exhibit weaknesses in being less meticulous and inventive, showing less interest in speculative or spontaneous ideas, and while firm and objective, they are noted for not being particularly kindly and warm.</t>
+  </si>
+  <si>
+    <t>This cluster describes individuals who are highly social and meticulously prepared, driven by a thoughtful and vigilant nature, yet they grapple with emotional variability and a tendency towards direct, sometimes careless, exuberance. Their strengths are evident in their exceptional planning and preparedness, making them reliably ready for challenges, complemented by their social and engaging demeanor, kindly warmth, and unwavering stability. However, they exhibit notable weaknesses in their intellectual expression and creative spontaneity, often finding abstract ideas challenging and lacking an interest in others' deeper emotions, compounded by a highly variable temper that leads to unpredictable mood shifts and a tendency to be direct and somewhat careless in social settings.</t>
+  </si>
+  <si>
+    <t>This cluster describes individuals who are typically lively and imaginative, preferring to be at the center of attention, though they can also be prone to emotional fluctuations. Their key strengths lie in their high levels of exuberance and directness, making them the life of the party, coupled with a highly imaginative and conceptual mind that constantly generates fresh and excellent ideas. However, they exhibit weaknesses in being less self-possessed and systematic, often lacking order, and tending to be less kindly and warm, which is compounded by a slightly variable and unpredictable temper.</t>
+  </si>
+  <si>
+    <t>What does it mean for a person to be social innovator?</t>
+  </si>
+  <si>
+    <t>What does it mean for a person to be responsible preparer?</t>
+  </si>
+  <si>
+    <t>What does it mean for a person to be social stabilizer?</t>
+  </si>
+  <si>
+    <t>What does it mean for a person to be systematic friend?</t>
+  </si>
+  <si>
+    <t>What does it mean for a persom to be engaging organizer?</t>
+  </si>
+  <si>
+    <t>What does it mean for a person to be spirited creator?</t>
   </si>
   <si>
     <t>Fantastic! That’s exactly what I needed. Now, let’s return to your analysis. Your next task is to describe a specific person based on the provided information. Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the person. The first sentence should use varied language to give an overview of the person. The second sentence should describe the person's specific strengths based on the metrics. The third sentence should describe aspects in which the person is average and/or weak based on the statistics. Finally, summarize the person with a single concluding statement.
-Here is the statistical description of the person: ```Person №7 is average on social and engaging. Person №7 is quite high on carefree and practical. Person №7 is average on unassuming and orderly. Person №7 is quite low on articulate intellect. Person №7 is average on self-reliant and systematic. Person №7 is average on methodical and diligent. Person №7 is average on creative and inventive. Person №7 is quite high on concrete and routine. Person №7 is quite high on proactive and organized. Person №7 is average on calm demeanor. Person №7 is quite low on compassionate. Person №7 is average on steady and composed. ´´´ 
-Here is the informative description of a person belongs to: ```Person №7 is practical innovator with the following characteristics: This cluster describes individuals who are highly sociable and creatively inventive, preferring methodical and practical approaches, and maintaining a calm demeanor despite internal emotional shifts.
-Their strengths are evident in their engaging social presence, their abundant and inventive ideas often applied in a thoughtful and practical manner, and their diligent, structured approach to tasks, all supported by a generally unruffled disposition.
-A significant weakness, however, is their relatively low level of steadiness and composure, indicating that their moods can often shift dramatically.´´´</t>
-  </si>
-  <si>
-    <t>Person №7 is a highly proactive and organized individual who embraces a practical and routine-focused approach to life, often remaining unworried by abstract complexities. Their strengths include a strong sense of being carefree and practical, a preference for concrete and routine methods, and a notable drive to be proactive and organized, ensuring tasks are managed efficiently. However, they are quite low in articulate intellect and compassion, and exhibit only average levels of social engagement, methodical diligence, and creative inventiveness, while maintaining a calm demeanor. Ultimately, Person №7 is a reliable and structured individual who prioritizes tangible results and order, though they may not be known for profound verbal expression or deep emotional connection.</t>
-  </si>
-  <si>
-    <t>Here is the statistical description of the person: ```Person №18 is quite low on private and sensitive. Person №18 is very low on thoughtful and visionary. In particular, Person №18 indicates that they have excellent ideas. Person №18 is quite low on unassuming and orderly. Person №18 is average on caring and down-to-earth. Person №18 is very high on concerned and prudent. In particular, Person №18 indicates that they worry about things. Person №18 is quite low on easygoing and flexible. Person №18 is average on verbal and literal. Person №18 is quite high on concrete and routine. Person №18 is average on proactive and organized. Person №18 is average on responsive psyche. Person №18 is quite low on compassionate. Person №18 is quite high on fluid and shifting. ´´´ 
-Here is the informative description of a person belongs to: ```Person №18 is prudent organizer with the following characteristics: This cluster describes individuals who are less reserved and more prone to worry, balancing a degree of conscientiousness with a less empathetic and emotionally stable state.
-Their strengths include being less private or easily irritated, a tendency to be more proactive and organized, and a reduced likelihood of being messy or shirking duties.
-However, they frequently find themselves pondering and worrying, are less compassionate and thoughtful, exhibit less stable moods, and may not be as articulate or quick to grasp complex ideas.´´´</t>
-  </si>
-  <si>
-    <t>Person №18 is a diligent yet often anxious individual who thrives on routine and concrete thinking, though their emotional state can be quite changeable. Their strengths include a less private nature, a methodical adherence to responsibilities, and a highly prudent approach to anticipating potential concerns, suggesting a reliable and conscientious character. However, they are significantly lacking in imaginative and visionary ideas, show low compassion, and exhibit frequent, fluid mood shifts. Overall, Person №18 is a practical and conscientious worrier who prefers structure and anticipates problems, but struggles with creativity, emotional warmth, and consistent emotional stability.</t>
-  </si>
-  <si>
-    <t>Thats really good. You truly understand the factors and names. 
-Now your task is to provide a description of a cluster.
-Please use the statistical description enclosed with ``` ´´´ . It provides information about the cluster based on the latent factors that most accurately describe it.
-For each cluster, write a concise summary based on the available information.
-The first sentence should give an overview of the cluster. 
-The second sentence should describe the cluster’s specific strengths based on the available information.
-The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-I will provided you with the cluster description and you will return the summary. 
-Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:```Members of this cluster can be described as:  relatively high on social and engaging,  normal on thoughtful and visionary,  normal on unassuming and orderly,  normal on caring and down-to-earth,  normal on self-reliant and systematic,  slightly high on methodical and diligent,  relatively high on creative and inventive,  slightly high on concrete and routine,  normal on proactive and organized,  relatively high on calm demeanor,  normal on compassionate,  relatively low on steady and composed´´´</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are highly sociable and creatively inventive, preferring methodical and practical approaches, and maintaining a calm demeanor despite internal emotional shifts.
-Their strengths are evident in their engaging social presence, their abundant and inventive ideas often applied in a thoughtful and practical manner, and their diligent, structured approach to tasks, all supported by a generally unruffled disposition.
-A significant weakness, however, is their relatively low level of steadiness and composure, indicating that their moods can often shift dramatically.</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are less reserved and more prone to worry, balancing a degree of conscientiousness with a less empathetic and emotionally stable state.
-Their strengths include being less private or easily irritated, a tendency to be more proactive and organized, and a reduced likelihood of being messy or shirking duties.
-However, they frequently find themselves pondering and worrying, are less compassionate and thoughtful, exhibit less stable moods, and may not be as articulate or quick to grasp complex ideas.</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are outwardly social, practical, and highly organized, yet they grapple with an internal tension between a calm demeanor and frequently shifting moods, often experiencing concern despite a generally carefree exterior.
-Their strengths lie in their strong social engagement, vivaciousness, and proactive, organized approach to life, ensuring they are prepared and thrive in structured, concrete environments.
-However, they are prone to worry and internal mood shifts, exhibiting a relative inflexibility, and their literal nature means they are less inclined towards abstract or imaginative thinking.</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are highly energetic, outgoing, and brimming with creative ideas, though they may face challenges in systematic organization and emotional consistency.
-Their strengths lie in their vivacious and outspoken nature, making them the life of the party and confidently expressive, combined with a remarkable ability to generate inventive and excellent ideas.
-However, they exhibit weaknesses in being self-reliant and systematic, potentially leading to disorganization, coupled with less articulate intellectual expression, lower compassion, and a tendency for their moods to shift frequently.</t>
+Here is the statistical description of the person:
+```Person №3 is quite low on private and sensitive. Person №3 is average on meticulous and inventive. Person №3 is very high on exuberant and direct. In particular, Person №3 indicates that they leave their belongings around. Person №3 is average on empathetic and concrete. Person №3 is very high on thoughtful and vigilant. In particular, Person №3 indicates that they worry about things. Person №3 is average on planned and prepared. Person №3 is very low on articulate and literal. In particular, Person №3 indicates that they do not have a good imagination. Person №3 is very high on observant and routine. In particular, Person №3 indicates that they follow a schedule. Person №3 is quite high on foresighted and cautious. Person №3 is quite low on impressionable and reactive. Person №3 is very low on kindly and warm. In particular, Person №3 indicates that they have a soft heart. Person №3 is quite high on variable temper. ´´´ 
+Here is the informative description of a person belongs to: ```Person №3 is social stabilizer with the following characteristics: This cluster describes individuals who are socially engaging and well-prepared, embodying a stable yet sometimes unpredictable demeanor, with a preference for practical rather than abstract thought.
+Their specific strengths include their high sociability and engaging nature, consistently being foresighted and cautious in preparation, and maintaining an unflappable and stable temperament, while also showing empathy and a preference for concrete ideas.
+However, they exhibit weaknesses in being prone to worrying, can struggle with abstract ideas and a vivid imagination, and are characterized by a relatively high variable temper, suggesting unpredictable mood shifts.´´´</t>
+  </si>
+  <si>
+    <t>Person №3 is an outgoing and highly watchful individual who embraces routine and preparedness, yet grapples with internal emotional fluctuations and a less imaginative, more literal outlook. Their strengths include being very high in exuberance and directness, which makes them the life of the party, alongside being quite foresighted and cautious, ensuring they are always prepared, and not easily disturbed. However, they are notably prone to worrying and exhibit a very low capacity for imagination and abstract thought, preferring strict routines, are very low in kindness and warmth, and experience frequent, shifting moods. In essence, Person №3 is a highly social and prepared individual who prioritizes routine and practicality, but struggles with emotional consistency and imaginative depth.</t>
+  </si>
+  <si>
+    <t>Here is the statistical description of the person: ```Person №18 is quite low on private and sensitive. Person №18 is very low on meticulous and inventive. In particular, Person №18 indicates that they have excellent ideas. Person №18 is quite low on humble and orderly. Person №18 is average on empathetic and concrete. Person №18 is very high on thoughtful and vigilant. In particular, Person №18 indicates that they worry about things. Person №18 is quite low on easygoing and casual. Person №18 is average on articulate and literal. Person №18 is quite high on observant and routine. Person №18 is average on foresighted and cautious. Person №18 is average on impressionable and reactive. Person №18 is quite low on kindly and warm. Person №18 is quite high on variable temper. ´´´ Here is the informative description of a person belongs to: ```Person №18 is responsible preparer with the following characteristics: This cluster describes individuals who are often preoccupied with worries, generally less private, and tend to be quite responsible, though not always warm or even-tempered. Their strengths include a thoughtful and vigilant nature, indicating attentiveness to potential issues, coupled with a tendency to be more prepared and responsible rather than casual or impulsive. However, they exhibit weaknesses in being less private and sensitive, less humble or orderly in their interactions, less intellectually expressive, less kindly or warm, and are prone to a more variable temper.´´´</t>
+  </si>
+  <si>
+    <t>Person №18 is an individual characterized by significant worries and a tendency for emotional fluctuations, who prefers routine and a practical approach, yet struggles with inventiveness and warmth. Their strengths lie in their very high thoughtful and vigilant nature, meaning they are highly conscientious and attentive to potential issues, alongside a clear preference for order and responsibility, indicated by being quite low on easygoing and casual. However, they are notably weak in generating excellent ideas and inventive thought, quite low in being humble and orderly, and not particularly kindly or warm, while also exhibiting a quite high and often variable temper. In summary, Person №18 is a diligent but anxious person who values structure and anticipates problems, yet struggles with creative spontaneity, emotional consistency, and expressing warmth.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -390,6 +368,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -735,11 +725,13 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1097,11 +1089,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="62.453125" customWidth="1"/>
-    <col min="2" max="2" width="128.90625" customWidth="1"/>
+    <col min="1" max="1" width="88.7265625" customWidth="1"/>
+    <col min="2" max="2" width="94.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -1112,261 +1104,313 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="4" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="6" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="9" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="10" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="11" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="12" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="13" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="14" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+    <row r="15" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+    <row r="16" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+    <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="A18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+    <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+    <row r="23" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+    <row r="24" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+    <row r="25" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="333.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" ht="60" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="40" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="50" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="50" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="60" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="50" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B31" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="210" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="3" t="s">
+      <c r="B32" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="3" t="s">
+    <row r="33" spans="1:2" ht="120" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="145" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B31" s="3" t="s">
+      <c r="B33" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="362.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>60</v>
-      </c>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/describe/few_shot/final_summary/messages_personality.xlsx
+++ b/data/describe/few_shot/final_summary/messages_personality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\final_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D838DE5-07C9-4A9E-B0BB-FC69FFE86AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BAD0D52-A65F-4F8D-84C4-7A5AE9DDE85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31005" yWindow="2295" windowWidth="29250" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="messages_personality1.xlsx" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>User</t>
   </si>
@@ -33,208 +33,125 @@
     <t>Assistant</t>
   </si>
   <si>
-    <t>What does it mean when a person is described as private and sensitive?</t>
-  </si>
-  <si>
-    <t>Someone who is private and sensitive might find themselves easily irritated, preferring to keep to themselves and showing little interest in others. This person also tends to feel blue and can get upset quite easily.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as social and engaging?</t>
-  </si>
-  <si>
-    <t>A social and engaging person absolutely thrives in company, effortlessly feeling comfortable around people and striking up conversations with many at parties. They love to kick off discussions, often becoming the heart of the party, and genuinely enjoy learning about others.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as meticulous and inventive?</t>
-  </si>
-  <si>
-    <t>A meticulous and inventive person is absolutely bursting with excellent ideas and possesses a truly vivid imagination, often found brimming with new thoughts. They tend to worry about things and pay careful attention to all the little details.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as broad-minded and practical?</t>
-  </si>
-  <si>
-    <t>A person described as broad-minded and practical is not one to fret over things, nor do they often get lost in a vivid imagination or constantly burst forth with new concepts. Instead, they tend to be less focused on generating brilliant ideas or getting caught up in the minutiae of details.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as humble and orderly?</t>
-  </si>
-  <si>
-    <t>Humble and orderly individuals prefer to stay out of the spotlight, getting their chores done promptly, and maintaining a calm demeanor, especially when meeting new people. They also make a point of taking time out for others, demonstrating a considerate and composed nature.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as exuberant and direct?</t>
-  </si>
-  <si>
-    <t>When a person is described as exuberant and direct, they are often the life of the party and aren't afraid to speak their mind, even if it means occasionally insulting someone. You might also notice they have a habit of forgetting to put things back in their place, leaving belongings scattered, and generally making a bit of a mess.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as intellectual and expressive?</t>
-  </si>
-  <si>
-    <t>A person described as intellectual and expressive boasts a rich vocabulary, often utilizing difficult words to articulate their abundant ideas and quickly grasp new concepts. They are full of innovative thoughts, though their focus on ideas might mean they aren't always deeply interested in the feelings or experiences of others.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as empathetic and concrete?</t>
-  </si>
-  <si>
-    <t>An empathetic and concrete person truly feels and sympathizes with the emotions of others, always ready to take time out to help. They tend to shy away from abstract concepts, preferring to focus on practical, real-world ideas.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as self-possessed and systematic?</t>
-  </si>
-  <si>
-    <t>A self-possessed and systematic individual often comes across as quite relaxed, showing little interest in others or their problems. They are also known for liking order and are comfortable initiating conversations.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as thoughtful and vigilant?</t>
-  </si>
-  <si>
-    <t>When a person is described as thoughtful and vigilant, it means they are often someone who finds themselves wrapped up in worrying about various matters.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as easygoing and casual?</t>
-  </si>
-  <si>
-    <t>An easygoing and casual person might often forget where things go, leading to a bit of a mess and belongings left scattered around. They generally carry a relaxed demeanor, though they might occasionally shirk their duties.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as planned and prepared?</t>
-  </si>
-  <si>
-    <t>A person who is planned and prepared loves to stick to a schedule and tackles their chores without delay. They are also the kind of individual who is always ready for whatever comes their way.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as articulate and literal?</t>
-  </si>
-  <si>
-    <t>Someone described as articulate and literal possesses a rich vocabulary and enjoys using complex words to express themselves. Yet, when it comes to creativity, their imagination isn't particularly strong.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as imaginative and conceptual?</t>
-  </si>
-  <si>
-    <t>Someone who is imaginative and conceptual is truly a fount of creativity, always bubbling with a vivid imagination. They are also brimming with excellent and fresh ideas, constantly generating new thoughts and concepts.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as speculative and spontaneous?</t>
-  </si>
-  <si>
-    <t>A speculative and spontaneous person doesn't shy away from abstract ideas, finding them easy to understand and being genuinely interested in them, and they often possess a good imagination. You won't find them rigidly sticking to a schedule, as they prefer a more flexible approach to life.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as observant and routine?</t>
-  </si>
-  <si>
-    <t>When a person is described as observant and routine, they might find abstract ideas a bit of a puzzle and aren't typically known for a wild imagination. Instead, they prefer the comfort of sticking to a clear schedule and generally aren't very interested in exploring complex, abstract concepts.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as impromptu and bold?</t>
-  </si>
-  <si>
-    <t>When a person is described as impromptu and bold, it means they are not always prepared for what's ahead.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as foresighted and cautious?</t>
-  </si>
-  <si>
-    <t>When a person is described as foresighted and cautious, it means they are the kind of individual who is always prepared for what lies ahead.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as impressionable and reactive?</t>
-  </si>
-  <si>
-    <t>When a person is described as impressionable and reactive, it means they tend to be quite easily disturbed by things.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as unflappable and stable?</t>
-  </si>
-  <si>
-    <t>When a person is described as unflappable and stable, it means they are not easily disturbed by external events and maintain a calm demeanor even in challenging situations. This reliability suggests they approach life with a sense of consistency and steadiness, making them a soothing presence to those around them.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as kindly and warm?</t>
-  </si>
-  <si>
-    <t>When a person is described as kindly and warm, it means they tend to have a gentle and compassionate nature, showing care for othersâ€”even if those traits are not predominantly defined by strong characteristics. In contrast, they are not firm and objective, suggesting they may prioritize empathy and understanding over strictness or detachment.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as firm and objective?</t>
-  </si>
-  <si>
-    <t>When a person is described as firm and objective, it means they are not kindly and warm. They tend to approach situations with a level-headed and logical perspective, often making decisions based on facts rather than emotions, and can be unwavering in their stance.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as even temper?</t>
-  </si>
-  <si>
-    <t>When a person is described as having an even temper, it means they are not prone to mood swings or emotional ups and downs. They maintain a steady and calm demeanor, remaining composed even in situations that might provoke strong feelings in others.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as variable temper?</t>
-  </si>
-  <si>
-    <t>When a person is described as having a variable temper, it means they often find their mood shifting unpredictably. This can make their emotional responses feel a bit like a rollercoaster, keeping others on their toes and unsure of what to expect from them.</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are highly sociable, imaginatively conceptual, and remarkably stable, though they may experience some emotional fluctuations. Their strengths shine through in their strong social engagement, a rich and imaginative conceptual mind that generates fresh ideas, and a notably unflappable and stable demeanor that keeps them calm and consistent. They also possess a slight inclination towards being planned and prepared. However, a relative weakness lies in their less even temper, suggesting they may be more prone to mood swings, and despite their imagination, they also show a slight tendency towards being observant and routine, which might imply a subtle disconnect in fully embracing abstract concepts.</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are often preoccupied with worries, generally less private, and tend to be quite responsible, though not always warm or even-tempered. Their strengths include a thoughtful and vigilant nature, indicating attentiveness to potential issues, coupled with a tendency to be more prepared and responsible rather than casual or impulsive. However, they exhibit weaknesses in being less private and sensitive, less humble or orderly in their interactions, less intellectually expressive, less kindly or warm, and are prone to a more variable temper.</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are socially engaging and well-prepared, embodying a stable yet sometimes unpredictable demeanor, with a preference for practical rather than abstract thought. Their specific strengths include their high sociability and engaging nature, consistently being foresighted and cautious in preparation, and maintaining an unflappable and stable temperament, while also showing empathy and a preference for concrete ideas. However, they exhibit weaknesses in being prone to worrying, can struggle with abstract ideas and a vivid imagination, and are characterized by a relatively high variable temper, suggesting unpredictable mood shifts.</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are sociable and well-organized, demonstrating a stable and prepared approach to life, though they are less inclined towards abstract thought or intense imagination. Their specific strengths include being socially engaging, empathetically concrete, humble and orderly, and reliably planned and prepared, all supported by an unflappable and even-tempered nature. However, they exhibit weaknesses in being less meticulous and inventive, showing less interest in speculative or spontaneous ideas, and while firm and objective, they are noted for not being particularly kindly and warm.</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are highly social and meticulously prepared, driven by a thoughtful and vigilant nature, yet they grapple with emotional variability and a tendency towards direct, sometimes careless, exuberance. Their strengths are evident in their exceptional planning and preparedness, making them reliably ready for challenges, complemented by their social and engaging demeanor, kindly warmth, and unwavering stability. However, they exhibit notable weaknesses in their intellectual expression and creative spontaneity, often finding abstract ideas challenging and lacking an interest in others' deeper emotions, compounded by a highly variable temper that leads to unpredictable mood shifts and a tendency to be direct and somewhat careless in social settings.</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are typically lively and imaginative, preferring to be at the center of attention, though they can also be prone to emotional fluctuations. Their key strengths lie in their high levels of exuberance and directness, making them the life of the party, coupled with a highly imaginative and conceptual mind that constantly generates fresh and excellent ideas. However, they exhibit weaknesses in being less self-possessed and systematic, often lacking order, and tending to be less kindly and warm, which is compounded by a slightly variable and unpredictable temper.</t>
-  </si>
-  <si>
-    <t>What does it mean for a person to be social innovator?</t>
-  </si>
-  <si>
-    <t>What does it mean for a person to be responsible preparer?</t>
-  </si>
-  <si>
-    <t>What does it mean for a person to be social stabilizer?</t>
-  </si>
-  <si>
-    <t>What does it mean for a person to be systematic friend?</t>
-  </si>
-  <si>
-    <t>What does it mean for a persom to be engaging organizer?</t>
-  </si>
-  <si>
-    <t>What does it mean for a person to be spirited creator?</t>
-  </si>
-  <si>
-    <t>Fantastic! That’s exactly what I needed. Now, let’s return to your analysis. Your next task is to describe a specific person based on the provided information. Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the person. The first sentence should use varied language to give an overview of the person. The second sentence should describe the person's specific strengths based on the metrics. The third sentence should describe aspects in which the person is average and/or weak based on the statistics. Finally, summarize the person with a single concluding statement.
-Here is the statistical description of the person:
-```Person №3 is quite low on private and sensitive. Person №3 is average on meticulous and inventive. Person №3 is very high on exuberant and direct. In particular, Person №3 indicates that they leave their belongings around. Person №3 is average on empathetic and concrete. Person №3 is very high on thoughtful and vigilant. In particular, Person №3 indicates that they worry about things. Person №3 is average on planned and prepared. Person №3 is very low on articulate and literal. In particular, Person №3 indicates that they do not have a good imagination. Person №3 is very high on observant and routine. In particular, Person №3 indicates that they follow a schedule. Person №3 is quite high on foresighted and cautious. Person №3 is quite low on impressionable and reactive. Person №3 is very low on kindly and warm. In particular, Person №3 indicates that they have a soft heart. Person №3 is quite high on variable temper. ´´´ 
-Here is the informative description of a person belongs to: ```Person №3 is social stabilizer with the following characteristics: This cluster describes individuals who are socially engaging and well-prepared, embodying a stable yet sometimes unpredictable demeanor, with a preference for practical rather than abstract thought.
-Their specific strengths include their high sociability and engaging nature, consistently being foresighted and cautious in preparation, and maintaining an unflappable and stable temperament, while also showing empathy and a preference for concrete ideas.
-However, they exhibit weaknesses in being prone to worrying, can struggle with abstract ideas and a vivid imagination, and are characterized by a relatively high variable temper, suggesting unpredictable mood shifts.´´´</t>
-  </si>
-  <si>
-    <t>Person №3 is an outgoing and highly watchful individual who embraces routine and preparedness, yet grapples with internal emotional fluctuations and a less imaginative, more literal outlook. Their strengths include being very high in exuberance and directness, which makes them the life of the party, alongside being quite foresighted and cautious, ensuring they are always prepared, and not easily disturbed. However, they are notably prone to worrying and exhibit a very low capacity for imagination and abstract thought, preferring strict routines, are very low in kindness and warmth, and experience frequent, shifting moods. In essence, Person №3 is a highly social and prepared individual who prioritizes routine and practicality, but struggles with emotional consistency and imaginative depth.</t>
-  </si>
-  <si>
-    <t>Here is the statistical description of the person: ```Person №18 is quite low on private and sensitive. Person №18 is very low on meticulous and inventive. In particular, Person №18 indicates that they have excellent ideas. Person №18 is quite low on humble and orderly. Person №18 is average on empathetic and concrete. Person №18 is very high on thoughtful and vigilant. In particular, Person №18 indicates that they worry about things. Person №18 is quite low on easygoing and casual. Person №18 is average on articulate and literal. Person №18 is quite high on observant and routine. Person №18 is average on foresighted and cautious. Person №18 is average on impressionable and reactive. Person №18 is quite low on kindly and warm. Person №18 is quite high on variable temper. ´´´ Here is the informative description of a person belongs to: ```Person №18 is responsible preparer with the following characteristics: This cluster describes individuals who are often preoccupied with worries, generally less private, and tend to be quite responsible, though not always warm or even-tempered. Their strengths include a thoughtful and vigilant nature, indicating attentiveness to potential issues, coupled with a tendency to be more prepared and responsible rather than casual or impulsive. However, they exhibit weaknesses in being less private and sensitive, less humble or orderly in their interactions, less intellectually expressive, less kindly or warm, and are prone to a more variable temper.´´´</t>
-  </si>
-  <si>
-    <t>Person №18 is an individual characterized by significant worries and a tendency for emotional fluctuations, who prefers routine and a practical approach, yet struggles with inventiveness and warmth. Their strengths lie in their very high thoughtful and vigilant nature, meaning they are highly conscientious and attentive to potential issues, alongside a clear preference for order and responsibility, indicated by being quite low on easygoing and casual. However, they are notably weak in generating excellent ideas and inventive thought, quite low in being humble and orderly, and not particularly kindly or warm, while also exhibiting a quite high and often variable temper. In summary, Person №18 is a diligent but anxious person who values structure and anticipates problems, yet struggles with creative spontaneity, emotional consistency, and expressing warmth.</t>
+    <t>What does it mean when a person is described as sensitive and private?</t>
+  </si>
+  <si>
+    <t>When a person is described as sensitive and private, they often aren't very interested in others and can easily get irritated. These individuals also tend to be quiet, prefer to keep in the background around strangers, and generally have little to say.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as engaging and sociable?</t>
+  </si>
+  <si>
+    <t>When a person is described as engaging and sociable, it means they feel very comfortable around others, often taking the lead to start conversations and chat with many different people at parties. They are genuinely interested in the people around them and frequently become the life of the party.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as thoughtful and imaginative?</t>
+  </si>
+  <si>
+    <t>A thoughtful and imaginative person tends to worry about things and can get stressed out easily, often because they possess a very vivid imagination. They are truly brimming with excellent ideas and are constantly full of new thoughts.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as not anxious and carefree?</t>
+  </si>
+  <si>
+    <t>A person described as not anxious and carefree isn't prone to worrying or getting stressed out easily. They also don't tend to have a vivid imagination, excellent ideas, or be constantly full of new thoughts, indicating a more relaxed and less preoccupied state.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as discreet and diligent?</t>
+  </si>
+  <si>
+    <t>A discreet and diligent person strongly prefers to stay out of the limelight, making sure their chores are done right away, and always setting aside time for others. They also tend to be quiet when meeting new people and appreciate things being in their proper place.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as carefree and spontaneous?</t>
+  </si>
+  <si>
+    <t>A carefree and spontaneous person might occasionally insult others without much thought, and you'll often find their belongings scattered as they tend to forget putting things back or shirk their duties. However, they are also known for being the vibrant life of the party!</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as insightful and reserved?</t>
+  </si>
+  <si>
+    <t>A person described as insightful and reserved is often brimming with original thoughts and excellent ideas, often expressed with a rich vocabulary. While intellectually vibrant, they tend to keep to themselves, not showing much interest in other people's problems or feelings.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as empathetic and considerate?</t>
+  </si>
+  <si>
+    <t>When someone is described as empathetic and considerate, it means they truly feel and sympathize with the emotions of those around them. They are also known for taking the time to be there for others, offering their support and understanding.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as practical and grounded?</t>
+  </si>
+  <si>
+    <t>A practical and grounded person isn't particularly interested in abstract ideas and may find them hard to grasp, often coupled with not having a very vivid imagination. You'll find them relaxed most of the time, and they're usually the ones to start conversations.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as not practical and speculative?</t>
+  </si>
+  <si>
+    <t>A person described as not practical and speculative is someone who loves to dive into abstract ideas and possesses a good imagination. They easily grasp complex concepts and may not always be relaxed, often preferring others to initiate conversations.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as disorganized and laid-back?</t>
+  </si>
+  <si>
+    <t>When you describe someone as disorganized and laid-back, imagine a person who often creates a bit of a mess, frequently forgets to put things away, and has a habit of leaving their belongings scattered. They might even shirk their duties from time to time, but you'll usually find them quite relaxed and easygoing.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as organized and punctual?</t>
+  </si>
+  <si>
+    <t>When a person is described as organized and punctual, it means they have a knack for getting things done efficiently, often completing chores right away and sticking to a schedule. They approach life with a prepared mindset, ensuring they are always ready for what comes next!</t>
+  </si>
+  <si>
+    <t>Members of this cluster can be described as naturally engaging and sociable, making them approachable and charming in various social settings. Their strengths lie in their ability to connect with others easily and their organizational skills, which suggest they can manage tasks effectively. However, they may struggle with being discreet and diligent at times, and their slightly lower practical orientation could hinder their ability to navigate certain real-world challenges effectively.</t>
+  </si>
+  <si>
+    <t>This cluster comprises individuals who display a balance of traits, showing an average level of creativity and spontaneity while being less sensitive and private. Their strengths lie in their empathetic and considerate nature, which allows for meaningful interactions with others, alongside a good level of thoughtfulness and imagination. However, they may struggle with aspects of their personal boundaries and occasional disorganization, indicating a somewhat relaxed stance that could lead to challenges in more structured environments.</t>
+  </si>
+  <si>
+    <t>This cluster is characterized by individuals who are vibrant and outgoing, displaying a strong sociability alongside a carefree attitude. Their specific strengths lie in their encouraging demeanor, empathy, and spontaneity, making them highly approachable and considerate of others' feelings. However, their extreme inclination towards being not practical and speculative may hinder their ability to focus on realistic goals and grounded decision-making.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as 
+social organizer?</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as balanced companion?</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as carefree planner?</t>
+  </si>
+  <si>
+    <t>Those were really good. Exactly what I am looking for. 
+Make sure you continue to use the same format and style in the next example. 
+I am now going to give you one last description task to complete. 
+You will receive information about the cluster based on the latent factors that best describe it.
+For each cluster, write a concise summary based on the available information.
+The first sentence should give an overview of the cluster. 
+The second sentence should describe the cluster’s specific strengths based on the available information.
+The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
+Now do the same thing with the following:
+Here is the statistical description of person №3: ```Person №3 is quite low on sensitive and private. Person №3 is average on thoughtful and imaginative. Person №3 is quite high on carefree and spontaneous. Person №3 is quite low on insightful and reserved. Person №3 is average on not practical and speculative. Person №3 is average on organized and punctual.´´´ 
+Here is the informative description of person: ```Person №3 is balanced companion with the following characteristics: This cluster represents individuals who maintain a balanced approach to life, characterized by their average levels of thoughtfulness and sociability, alongside a moderate sense of carefreeness. Their strengths lie in their empathetic nature and a spontaneous attitude, which makes them approachable and open to new experiences. However, this cluster may struggle with sensitivity and privacy, potentially leading to challenges in deeper emotional connections or personal boundaries.´´´</t>
+  </si>
+  <si>
+    <t>The individual identified as Person №3 embodies a unique blend of characteristics that suggest a balanced approach to life. They exhibit a notable strength in their carefree and spontaneous nature, making them approachable and open to embrace new experiences. On the other hand, they show weaknesses in sensitivity and privacy, which may hinder them from forming deep emotional connections or maintaining personal boundaries. Overall, this person represents a well-rounded companion who values both enjoyment and social interaction.</t>
+  </si>
+  <si>
+    <t>Here is the statistical description of Person №18: ```Person №18 is quite high on engaging and sociable. Person №18 is average on not anxious and carefree. Person №18 is average on carefree and spontaneous. Person №18 is quite low on insightful and reserved. Person №18 is average on not practical and speculative. Person №18 is very low on disorganized and laid-back. In particular, Person №18 indicates that they shirk their duties. ´´´ 
+Here is the informative description of : ```Person №18 is thoughtful companion with the following characteristics: This cluster is characterized by individuals who exhibit a balanced mix of sociability and emotional awareness, while generally maintaining a practical mindset. Their strengths lie in their ability to connect with others through thoughtfulness and spontaneity, enabling them to engage positively in social interactions. However, they may struggle with maintaining privacy and sensitivity, possibly leading to challenges in recognizing and addressing the deeper emotional needs of themselves and others.´´´</t>
+  </si>
+  <si>
+    <t>The individual identified as Person №18 stands out with a notable sociability and engaging demeanor. Their strengths are highlighted by their ability to connect with others through thoughtfulness and a willingness to be spontaneous in social situations. However, they exhibit weaknesses in being insightful and reserved, which may hinder their ability to address deeper emotional needs, both for themselves and those around them. Overall, Person №18 is a vibrant companion who actively engages with their social environment while striving to find a balance between spontaneity and emotional awareness.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -372,12 +289,6 @@
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -723,16 +634,19 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1089,11 +1003,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="88.7265625" customWidth="1"/>
-    <col min="2" max="2" width="94.90625" customWidth="1"/>
+    <col min="1" max="1" width="98" customWidth="1"/>
+    <col min="2" max="2" width="59.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -1104,127 +1018,127 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" ht="159" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="3" t="s">
+    </row>
+    <row r="15" spans="1:2" ht="61.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+    <row r="16" spans="1:2" ht="61.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:2" ht="170" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
@@ -1232,185 +1146,13 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" ht="80" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A25" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="60" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="40" x14ac:dyDescent="0.35">
-      <c r="A27" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="50" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="50" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="60" x14ac:dyDescent="0.35">
-      <c r="A30" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="50" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="210" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="120" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/describe/few_shot/final_summary/messages_personality.xlsx
+++ b/data/describe/few_shot/final_summary/messages_personality.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\final_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BAD0D52-A65F-4F8D-84C4-7A5AE9DDE85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F100CB41-FB83-49B4-8DDA-4DC36F5A02FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="messages_personality1.xlsx" sheetId="1" r:id="rId1"/>
+    <sheet name="QandA_data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>User</t>
   </si>
@@ -33,125 +33,107 @@
     <t>Assistant</t>
   </si>
   <si>
-    <t>What does it mean when a person is described as sensitive and private?</t>
-  </si>
-  <si>
-    <t>When a person is described as sensitive and private, they often aren't very interested in others and can easily get irritated. These individuals also tend to be quiet, prefer to keep in the background around strangers, and generally have little to say.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as engaging and sociable?</t>
-  </si>
-  <si>
-    <t>When a person is described as engaging and sociable, it means they feel very comfortable around others, often taking the lead to start conversations and chat with many different people at parties. They are genuinely interested in the people around them and frequently become the life of the party.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as thoughtful and imaginative?</t>
-  </si>
-  <si>
-    <t>A thoughtful and imaginative person tends to worry about things and can get stressed out easily, often because they possess a very vivid imagination. They are truly brimming with excellent ideas and are constantly full of new thoughts.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as not anxious and carefree?</t>
-  </si>
-  <si>
-    <t>A person described as not anxious and carefree isn't prone to worrying or getting stressed out easily. They also don't tend to have a vivid imagination, excellent ideas, or be constantly full of new thoughts, indicating a more relaxed and less preoccupied state.</t>
+    <t>What does it mean when a person is described as aloof and irritable?</t>
+  </si>
+  <si>
+    <t>When a person is described as aloof and irritable, it means they tend to be disinterested in others, often keeping to themselves and not engaging in conversation. They can be easily irritated and might come off as quiet or reserved around strangers, preferring to stay in the background and not share much about themselves.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as sociable and engaging?</t>
+  </si>
+  <si>
+    <t>When a person is described as sociable and engaging, it means they feel at ease in social settings and are eager to connect with others. They're the type who effortlessly strike up conversations, mingle with a variety of guests at gatherings, and often become the vibrant energy that lights up the party, showing genuine interest in the people around them.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as concerned and creative?</t>
+  </si>
+  <si>
+    <t>When a person is described as concerned and creative, it means they are deeply engaged with their thoughts and feelings, often worrying about various matters while also possessing a vivid imagination. They are likely to come up with excellent ideas and are brimming with creative potential, even as they may find themselves feeling stressed out by their own concerns.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as not concerned?</t>
+  </si>
+  <si>
+    <t>When a person is described as not concerned, it means they donâ€™t worry about things or get stressed out easily. Instead of being preoccupied with worries and bursting with ideas, they tend to approach life with a sense of calm and a steady mindset, allowing them to navigate challenges without the weight of anxiety.</t>
   </si>
   <si>
     <t>What does it mean when a person is described as discreet and diligent?</t>
   </si>
   <si>
-    <t>A discreet and diligent person strongly prefers to stay out of the limelight, making sure their chores are done right away, and always setting aside time for others. They also tend to be quiet when meeting new people and appreciate things being in their proper place.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as carefree and spontaneous?</t>
-  </si>
-  <si>
-    <t>A carefree and spontaneous person might occasionally insult others without much thought, and you'll often find their belongings scattered as they tend to forget putting things back or shirk their duties. However, they are also known for being the vibrant life of the party!</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as insightful and reserved?</t>
-  </si>
-  <si>
-    <t>A person described as insightful and reserved is often brimming with original thoughts and excellent ideas, often expressed with a rich vocabulary. While intellectually vibrant, they tend to keep to themselves, not showing much interest in other people's problems or feelings.</t>
+    <t>When a person is described as discreet and diligent, they often blend seamlessly into the background, preferring not to draw attention to themselves while getting things done efficiently and responsibly. They are attentive to the needs of others, take care of their obligations promptly, and maintain a sense of order, showcasing a thoughtful and reliable nature that reflects their quiet strength.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as vibrant and carefree?</t>
+  </si>
+  <si>
+    <t>When a person is described as vibrant and carefree, it means they have a lively and outgoing personality, often bringing energy and fun to social situations as they embrace being the life of the party. However, this carefree disposition may also lead to some recklessness, as they might forget where they put things or neglect certain responsibilities along the way.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as ideas and self-focused?</t>
+  </si>
+  <si>
+    <t>When a person is described as ideas and self-focused, it often means they are brimming with creativity and new thoughts, showing a strong inclination for coming up with innovative ideas. However, they may not pay much attention to others, feeling less interest in other people's problems or emotions, which can make them seem a bit distant in social situations.</t>
   </si>
   <si>
     <t>What does it mean when a person is described as empathetic and considerate?</t>
   </si>
   <si>
-    <t>When someone is described as empathetic and considerate, it means they truly feel and sympathize with the emotions of those around them. They are also known for taking the time to be there for others, offering their support and understanding.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as practical and grounded?</t>
-  </si>
-  <si>
-    <t>A practical and grounded person isn't particularly interested in abstract ideas and may find them hard to grasp, often coupled with not having a very vivid imagination. You'll find them relaxed most of the time, and they're usually the ones to start conversations.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as not practical and speculative?</t>
-  </si>
-  <si>
-    <t>A person described as not practical and speculative is someone who loves to dive into abstract ideas and possesses a good imagination. They easily grasp complex concepts and may not always be relaxed, often preferring others to initiate conversations.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as disorganized and laid-back?</t>
-  </si>
-  <si>
-    <t>When you describe someone as disorganized and laid-back, imagine a person who often creates a bit of a mess, frequently forgets to put things away, and has a habit of leaving their belongings scattered. They might even shirk their duties from time to time, but you'll usually find them quite relaxed and easygoing.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as organized and punctual?</t>
-  </si>
-  <si>
-    <t>When a person is described as organized and punctual, it means they have a knack for getting things done efficiently, often completing chores right away and sticking to a schedule. They approach life with a prepared mindset, ensuring they are always ready for what comes next!</t>
-  </si>
-  <si>
-    <t>Members of this cluster can be described as naturally engaging and sociable, making them approachable and charming in various social settings. Their strengths lie in their ability to connect with others easily and their organizational skills, which suggest they can manage tasks effectively. However, they may struggle with being discreet and diligent at times, and their slightly lower practical orientation could hinder their ability to navigate certain real-world challenges effectively.</t>
-  </si>
-  <si>
-    <t>This cluster comprises individuals who display a balance of traits, showing an average level of creativity and spontaneity while being less sensitive and private. Their strengths lie in their empathetic and considerate nature, which allows for meaningful interactions with others, alongside a good level of thoughtfulness and imagination. However, they may struggle with aspects of their personal boundaries and occasional disorganization, indicating a somewhat relaxed stance that could lead to challenges in more structured environments.</t>
-  </si>
-  <si>
-    <t>This cluster is characterized by individuals who are vibrant and outgoing, displaying a strong sociability alongside a carefree attitude. Their specific strengths lie in their encouraging demeanor, empathy, and spontaneity, making them highly approachable and considerate of others' feelings. However, their extreme inclination towards being not practical and speculative may hinder their ability to focus on realistic goals and grounded decision-making.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as 
-social organizer?</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as balanced companion?</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as carefree planner?</t>
-  </si>
-  <si>
-    <t>Those were really good. Exactly what I am looking for. 
-Make sure you continue to use the same format and style in the next example. 
-I am now going to give you one last description task to complete. 
-You will receive information about the cluster based on the latent factors that best describe it.
-For each cluster, write a concise summary based on the available information.
-The first sentence should give an overview of the cluster. 
-The second sentence should describe the cluster’s specific strengths based on the available information.
-The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-Now do the same thing with the following:
-Here is the statistical description of person №3: ```Person №3 is quite low on sensitive and private. Person №3 is average on thoughtful and imaginative. Person №3 is quite high on carefree and spontaneous. Person №3 is quite low on insightful and reserved. Person №3 is average on not practical and speculative. Person №3 is average on organized and punctual.´´´ 
-Here is the informative description of person: ```Person №3 is balanced companion with the following characteristics: This cluster represents individuals who maintain a balanced approach to life, characterized by their average levels of thoughtfulness and sociability, alongside a moderate sense of carefreeness. Their strengths lie in their empathetic nature and a spontaneous attitude, which makes them approachable and open to new experiences. However, this cluster may struggle with sensitivity and privacy, potentially leading to challenges in deeper emotional connections or personal boundaries.´´´</t>
-  </si>
-  <si>
-    <t>The individual identified as Person №3 embodies a unique blend of characteristics that suggest a balanced approach to life. They exhibit a notable strength in their carefree and spontaneous nature, making them approachable and open to embrace new experiences. On the other hand, they show weaknesses in sensitivity and privacy, which may hinder them from forming deep emotional connections or maintaining personal boundaries. Overall, this person represents a well-rounded companion who values both enjoyment and social interaction.</t>
-  </si>
-  <si>
-    <t>Here is the statistical description of Person №18: ```Person №18 is quite high on engaging and sociable. Person №18 is average on not anxious and carefree. Person №18 is average on carefree and spontaneous. Person №18 is quite low on insightful and reserved. Person №18 is average on not practical and speculative. Person №18 is very low on disorganized and laid-back. In particular, Person №18 indicates that they shirk their duties. ´´´ 
-Here is the informative description of : ```Person №18 is thoughtful companion with the following characteristics: This cluster is characterized by individuals who exhibit a balanced mix of sociability and emotional awareness, while generally maintaining a practical mindset. Their strengths lie in their ability to connect with others through thoughtfulness and spontaneity, enabling them to engage positively in social interactions. However, they may struggle with maintaining privacy and sensitivity, possibly leading to challenges in recognizing and addressing the deeper emotional needs of themselves and others.´´´</t>
-  </si>
-  <si>
-    <t>The individual identified as Person №18 stands out with a notable sociability and engaging demeanor. Their strengths are highlighted by their ability to connect with others through thoughtfulness and a willingness to be spontaneous in social situations. However, they exhibit weaknesses in being insightful and reserved, which may hinder their ability to address deeper emotional needs, both for themselves and those around them. Overall, Person №18 is a vibrant companion who actively engages with their social environment while striving to find a balance between spontaneity and emotional awareness.</t>
+    <t>When a person is described as empathetic and considerate, it means they are in tune with the emotions of others, feeling what others feel and understanding their experiences. They also take the time to care for and support those around them, demonstrating kindness and thoughtfulness in their interactions.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as concrete and relaxed?</t>
+  </si>
+  <si>
+    <t>When a person is described as concrete and relaxed, it suggests they prefer straightforward ideas over complex concepts and generally maintain a calm demeanor. They may not engage much with imaginative thoughts and might find abstract notions challenging to grasp, lending to an overall sense of practicality and ease in their interactions.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as abstract and curious?</t>
+  </si>
+  <si>
+    <t>When a person is described as abstract and curious, they are not concrete and relaxed, indicating a vibrant imagination and a keen interest in exploring new ideas. They thrive on abstract thoughts and are always eager to discover and learn about the world around them, making them inquisitive and open-minded individuals.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as chaotic and forgetful?</t>
+  </si>
+  <si>
+    <t>When a person is described as chaotic and forgetful, it suggests that they tend to make a mess of things and often forget to put items back where they belong. This carefree attitude might lead them to leave their belongings scattered and even neglect their responsibilities, all while remaining pretty relaxed about the whole situation.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as organised and prompt?</t>
+  </si>
+  <si>
+    <t>When a person is described as organised and prompt, they are someone who values order and efficiency in their life. They make a habit of following a schedule, getting tasks done quickly, and always being ready for what lies ahead.</t>
+  </si>
+  <si>
+    <t>These individuals who exhibit a balanced personality, showing moderate traits in various areas. They have a strength in being abstract and curious, which suggests an openness to new ideas and creativity, along with an ability to empathize and be considerate towards others. However, they may experience weaknesses in their discretion and diligence, which could pose challenges in situations requiring focus and reliability.</t>
+  </si>
+  <si>
+    <t>These individuals who are predominantly sociable and engaging, exuding a vibrant and carefree aura. Their strengths lie in their ability to connect with others and maintain an uplifting energy, which fosters positive interactions. However, they may face challenges due to their slight lack of concern and creativity, potentially hindering their ability to address deeper issues and think outside the box.</t>
+  </si>
+  <si>
+    <t>Fantastic! That’s exactly what I needed. Now, let’s return to your analysis. Your next task is to describe a specific person based on the provided information. Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the person. The first sentence should use varied language to give an overview of the person. The second sentence should describe the person's specific strengths based on the metrics. The third sentence should describe aspects in which the person is average and/or weak based on the statistics. Finally, summarize the person with a single concluding statement. Here is the statistical description of Person №8: ```Person №8 is quite low on aloof and irritable. Person №8 is average on not concerned. Person №8 is quite high on vibrant and carefree. Person №8 is very high on empathetic and considerate. In particular, Person №8 has characteristics related to 'they sympathize with others feelings'. Person №8 is quite low on concrete and relaxed. Person №8 is average on organised and prompt. ´´´ Here is the informative description of Person №8: ```Person №8 is carefree organizer with the following characteristics: This cluster is characterized by individuals who exhibit a mix of vibrant and carefree attitudes, alongside a reasonable level of empathy and consideration for others. Their strengths lie in their ability to engage positively with their environment while being organized and punctual in their tasks. However, they may struggle with being creative and concerned, and their normal levels of aloofness might hinder deeper emotional connections with others.´´´</t>
+  </si>
+  <si>
+    <t>Person №8 is a vibrant individual known for their carefree spirit and strong sense of empathy towards others. Their specific strengths include being highly empathetic and considerate, allowing them to connect with others deeply and fostering positive interactions. However, they may experience challenges with creativity and express average concern for certain matters, which could affect their engagement in more complex emotional situations. Overall, Person №8 represents a cheerful and organized personality that combines spontaneity with a caring approach to relationships.</t>
+  </si>
+  <si>
+    <t>Here is the statistical description of Person №18: ```Person №18 is quite low on aloof and irritable. Person №18 is very low on concerned and creative. In particular, Person №18 has characteristics related to 'they get stressed out easily'. Person №18 is quite low on discreet and diligent. Person №18 is quite high on empathetic and considerate. Person №18 is very high on abstract and curious. Person №18 is quite low on chaotic and forgetful. ´´´ Here is the informative description of Person №18: ```Person №18 is balanced innovator with the following characteristics: This cluster consists of individuals who exhibit a balanced personality, showing moderate traits in various areas. They have a strength in being abstract and curious, which suggests an openness to new ideas and creativity, along with an ability to empathize and be considerate towards others. However, they may experience weaknesses in their discretion and diligence, which could pose challenges in situations requiring focus and reliability.´´´</t>
+  </si>
+  <si>
+    <t>Person №18 demonstrates a well-rounded personality characterized by a mix of inquisitive thinking and a strong sense of empathy. Their notable strengths include a high level of curiosity and the ability to connect thoughtfully with others, enhancing their interactions and creativity. However, they may encounter challenges such as a lack of focus and reliability, as indicated by their low scores in discretion and diligence. Overall, Person №18 embodies the essence of a balanced innovator, capable of generating fresh ideas while maintaining a compassionate demeanor.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as balanced innovator?</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as joyful connector?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -285,12 +267,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -634,19 +610,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1003,155 +970,147 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="98" customWidth="1"/>
-    <col min="2" max="2" width="59.453125" customWidth="1"/>
+    <col min="1" max="1" width="76.7265625" customWidth="1"/>
+    <col min="2" max="2" width="88.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="159" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="61.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+    </row>
+    <row r="17" spans="1:2" ht="174" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="61.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
+      <c r="B17" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="170" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="80" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
